--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterKH.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterKH.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:21:18+00:00</t>
+    <t>2025-02-10T11:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
